--- a/data/chapter2/FREDv3subset/Cleaned categoricals.xlsx
+++ b/data/chapter2/FREDv3subset/Cleaned categoricals.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="30" documentId="8_{60623660-2284-41AB-B886-16D1F90A32E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C0595D6-AD90-4E46-88AA-8749C7754999}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{D8EF4087-6677-49FB-9975-3CCCC10758D2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{D8EF4087-6677-49FB-9975-3CCCC10758D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="3" r:id="rId1"/>
